--- a/01_Data/02_Processed/Datos_hojas_excel_COL/18_nodos/03_Hidraulicos/VoluUtilDiarMasa_Jul26.xlsx
+++ b/01_Data/02_Processed/Datos_hojas_excel_COL/18_nodos/03_Hidraulicos/VoluUtilDiarMasa_Jul26.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\2. Universidad Nacional de Colombia\2. Postgraduate\1_SEMESTER\TESIS DE MAESTRIA\2nd Search\04_TESIS_DANIEL\03_CODIGO_TRABAJO_DANIEL\BESS_FACTS_master\01_Data\02_Processed\Datos_hojas_excel_COL\18_nodos\03_Hidraulicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99EF0ED2-9D08-4C0B-9C7B-AADE46F16E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78DD3A8-53B4-4D14-A3ED-CF65717578EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_LEEME" sheetId="1" r:id="rId1"/>
     <sheet name="01_SERIE" sheetId="2" r:id="rId2"/>
     <sheet name="02_POR_ENTIDAD" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_SERIE'!$A$1:$G$745</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -791,6 +794,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G745"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -826,7 +830,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -849,7 +853,7 @@
         <v>537110000</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -872,7 +876,7 @@
         <v>9140000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -895,7 +899,7 @@
         <v>359680000</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -918,7 +922,7 @@
         <v>597390000</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -941,7 +945,7 @@
         <v>410020000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -964,7 +968,7 @@
         <v>126290000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -987,7 +991,7 @@
         <v>1290490000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1010,7 +1014,7 @@
         <v>340300000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1033,7 +1037,7 @@
         <v>674360000</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1056,7 +1060,7 @@
         <v>61080000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1079,7 +1083,7 @@
         <v>127730000</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1102,7 +1106,7 @@
         <v>2880000</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1125,7 +1129,7 @@
         <v>975460000</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1148,7 +1152,7 @@
         <v>39740000</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1171,7 +1175,7 @@
         <v>30000000</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1194,7 +1198,7 @@
         <v>55040000</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1217,7 +1221,7 @@
         <v>442750000</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1240,7 +1244,7 @@
         <v>15590000</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1263,7 +1267,7 @@
         <v>99840000</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1286,7 +1290,7 @@
         <v>612600000</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1309,7 +1313,7 @@
         <v>135220000</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1332,7 +1336,7 @@
         <v>2243480000</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1355,7 +1359,7 @@
         <v>5790000</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1378,7 +1382,7 @@
         <v>672580000</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1401,7 +1405,7 @@
         <v>538650000</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1424,7 +1428,7 @@
         <v>10730000</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1447,7 +1451,7 @@
         <v>355320000</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1470,7 +1474,7 @@
         <v>588820000</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1493,7 +1497,7 @@
         <v>410670000</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1516,7 +1520,7 @@
         <v>129720000</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1539,7 +1543,7 @@
         <v>1317360000</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1562,7 +1566,7 @@
         <v>352470000</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1585,7 +1589,7 @@
         <v>685460000</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1608,7 +1612,7 @@
         <v>59800000</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1631,7 +1635,7 @@
         <v>127320000</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1654,7 +1658,7 @@
         <v>3220000</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1677,7 +1681,7 @@
         <v>972080000</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1700,7 +1704,7 @@
         <v>40090000</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1723,7 +1727,7 @@
         <v>38450000</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1746,7 +1750,7 @@
         <v>42040000</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1769,7 +1773,7 @@
         <v>442350000</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1792,7 +1796,7 @@
         <v>15110000</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1815,7 +1819,7 @@
         <v>97520000</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1838,7 +1842,7 @@
         <v>617710000</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1861,7 +1865,7 @@
         <v>135470000</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1884,7 +1888,7 @@
         <v>2226510000</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1907,7 +1911,7 @@
         <v>6840000</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1930,7 +1934,7 @@
         <v>672060000</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1953,7 +1957,7 @@
         <v>540550000</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1976,7 +1980,7 @@
         <v>12280000</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1999,7 +2003,7 @@
         <v>352370000</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2022,7 +2026,7 @@
         <v>607140000</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2045,7 +2049,7 @@
         <v>411310000</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2068,7 +2072,7 @@
         <v>131960000</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2091,7 +2095,7 @@
         <v>1377990000</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2114,7 +2118,7 @@
         <v>367500000</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2137,7 +2141,7 @@
         <v>693120000</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2160,7 +2164,7 @@
         <v>60550000</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2183,7 +2187,7 @@
         <v>127080000</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2206,7 +2210,7 @@
         <v>3390000</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2229,7 +2233,7 @@
         <v>969070000</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2252,7 +2256,7 @@
         <v>39770000</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2275,7 +2279,7 @@
         <v>23540000</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2298,7 +2302,7 @@
         <v>55840000</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2321,7 +2325,7 @@
         <v>442350000</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2344,7 +2348,7 @@
         <v>14730000</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2367,7 +2371,7 @@
         <v>95180000</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2390,7 +2394,7 @@
         <v>633160000</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2413,7 +2417,7 @@
         <v>136230000</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2436,7 +2440,7 @@
         <v>2241260000</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2459,7 +2463,7 @@
         <v>8910000</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2482,7 +2486,7 @@
         <v>678570000</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2505,7 +2509,7 @@
         <v>541710000</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2528,7 +2532,7 @@
         <v>14360000</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2551,7 +2555,7 @@
         <v>346410000</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2574,7 +2578,7 @@
         <v>638290000</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2597,7 +2601,7 @@
         <v>410880000</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2620,7 +2624,7 @@
         <v>133340000</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2643,7 +2647,7 @@
         <v>1421740000</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -2666,7 +2670,7 @@
         <v>382480000</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -2689,7 +2693,7 @@
         <v>697230000</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2712,7 +2716,7 @@
         <v>60620000</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -2735,7 +2739,7 @@
         <v>126670000</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2758,7 +2762,7 @@
         <v>4540000</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2781,7 +2785,7 @@
         <v>965520000</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2804,7 +2808,7 @@
         <v>38900000</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -2827,7 +2831,7 @@
         <v>32540000</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -2850,7 +2854,7 @@
         <v>43580000</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2873,7 +2877,7 @@
         <v>441940000</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -2896,7 +2900,7 @@
         <v>12940000</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -2919,7 +2923,7 @@
         <v>94590000</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -2942,7 +2946,7 @@
         <v>643320000</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -2965,7 +2969,7 @@
         <v>137420000</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -2988,7 +2992,7 @@
         <v>2255940000</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3011,7 +3015,7 @@
         <v>11290000</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -3034,7 +3038,7 @@
         <v>711970000</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3057,7 +3061,7 @@
         <v>544840000</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3080,7 +3084,7 @@
         <v>16070000</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3103,7 +3107,7 @@
         <v>341530000</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3126,7 +3130,7 @@
         <v>634900000</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -3149,7 +3153,7 @@
         <v>410880000</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -3172,7 +3176,7 @@
         <v>134910000</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -3195,7 +3199,7 @@
         <v>1451640000</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -3218,7 +3222,7 @@
         <v>388870000</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -3241,7 +3245,7 @@
         <v>698700000</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -3264,7 +3268,7 @@
         <v>122100000</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -3287,7 +3291,7 @@
         <v>252680000</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -3310,7 +3314,7 @@
         <v>4850000</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -3333,7 +3337,7 @@
         <v>1929580000</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -3356,7 +3360,7 @@
         <v>76380000</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -3379,7 +3383,7 @@
         <v>39070000</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -3402,7 +3406,7 @@
         <v>34070000</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -3425,7 +3429,7 @@
         <v>441940000</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -3448,7 +3452,7 @@
         <v>18680000</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -3471,7 +3475,7 @@
         <v>190980000</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -3494,7 +3498,7 @@
         <v>645490000</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -3517,7 +3521,7 @@
         <v>136040000</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -3540,7 +3544,7 @@
         <v>2246050000</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -3563,7 +3567,7 @@
         <v>24840000</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -3586,7 +3590,7 @@
         <v>716430000</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -3609,7 +3613,7 @@
         <v>546460000</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -3632,7 +3636,7 @@
         <v>17650000</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -3655,7 +3659,7 @@
         <v>337850000</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -3678,7 +3682,7 @@
         <v>608780000</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -3701,7 +3705,7 @@
         <v>410670000</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -3724,7 +3728,7 @@
         <v>136020000</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -3747,7 +3751,7 @@
         <v>1465440000</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -3770,7 +3774,7 @@
         <v>394160000</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -3793,7 +3797,7 @@
         <v>697770000</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -3816,7 +3820,7 @@
         <v>126120000</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -3839,7 +3843,7 @@
         <v>126010000</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -3862,7 +3866,7 @@
         <v>2600000</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -3885,7 +3889,7 @@
         <v>1924920000</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -3908,7 +3912,7 @@
         <v>73000000</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -3931,7 +3935,7 @@
         <v>31990000</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -3954,7 +3958,7 @@
         <v>42030000</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -3977,7 +3981,7 @@
         <v>442350000</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -4000,7 +4004,7 @@
         <v>20280000</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -4023,7 +4027,7 @@
         <v>191300000</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -4046,7 +4050,7 @@
         <v>646150000</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -4069,7 +4073,7 @@
         <v>136540000</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -4092,7 +4096,7 @@
         <v>2258070000</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -4115,7 +4119,7 @@
         <v>12710000</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -4138,7 +4142,7 @@
         <v>707360000</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -4161,7 +4165,7 @@
         <v>547880000</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -4184,7 +4188,7 @@
         <v>19100000</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -4207,7 +4211,7 @@
         <v>338230000</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -4230,7 +4234,7 @@
         <v>582460000</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -4253,7 +4257,7 @@
         <v>410670000</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -4276,7 +4280,7 @@
         <v>136120000</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -4299,7 +4303,7 @@
         <v>1476140000</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -4322,7 +4326,7 @@
         <v>397280000</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -4345,7 +4349,7 @@
         <v>696700000</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -4368,7 +4372,7 @@
         <v>64670000</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -4391,7 +4395,7 @@
         <v>125690000</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -4414,7 +4418,7 @@
         <v>3050000</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -4437,7 +4441,7 @@
         <v>961060000</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -4460,7 +4464,7 @@
         <v>34580000</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -4483,7 +4487,7 @@
         <v>23520000</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -4506,7 +4510,7 @@
         <v>41640000</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -4529,7 +4533,7 @@
         <v>441540000</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -4552,7 +4556,7 @@
         <v>18580000</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -4575,7 +4579,7 @@
         <v>96470000</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -4598,7 +4602,7 @@
         <v>645930000</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -4621,7 +4625,7 @@
         <v>137090000</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -4644,7 +4648,7 @@
         <v>2254930000</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -4667,7 +4671,7 @@
         <v>10600000</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -5242,7 +5246,7 @@
         <v>689260000</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -5265,7 +5269,7 @@
         <v>548400000</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -5288,7 +5292,7 @@
         <v>20940000</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -5311,7 +5315,7 @@
         <v>338620000</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -5334,7 +5338,7 @@
         <v>556530000</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -5357,7 +5361,7 @@
         <v>409160000</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -5380,7 +5384,7 @@
         <v>137190000</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -5403,7 +5407,7 @@
         <v>1502120000</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -5426,7 +5430,7 @@
         <v>421930000</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -5449,7 +5453,7 @@
         <v>697370000</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -5472,7 +5476,7 @@
         <v>131460000</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -5495,7 +5499,7 @@
         <v>250560000</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -5518,7 +5522,7 @@
         <v>2710000</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -5541,7 +5545,7 @@
         <v>956380000</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -5564,7 +5568,7 @@
         <v>76880000</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
@@ -5587,7 +5591,7 @@
         <v>48560000</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -5610,7 +5614,7 @@
         <v>53280000</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
@@ -5633,7 +5637,7 @@
         <v>440730000</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
@@ -5656,7 +5660,7 @@
         <v>10060000</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -5679,7 +5683,7 @@
         <v>195360000</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
@@ -5702,7 +5706,7 @@
         <v>647020000</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -5725,7 +5729,7 @@
         <v>132270000</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -5748,7 +5752,7 @@
         <v>2245140000</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -5771,7 +5775,7 @@
         <v>13300000</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -5794,7 +5798,7 @@
         <v>699960000</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
@@ -5817,7 +5821,7 @@
         <v>550380000</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -5840,7 +5844,7 @@
         <v>21950000</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -5863,7 +5867,7 @@
         <v>338940000</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
@@ -5886,7 +5890,7 @@
         <v>550960000</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
@@ -5909,7 +5913,7 @@
         <v>408310000</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
@@ -5932,7 +5936,7 @@
         <v>138270000</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
@@ -5955,7 +5959,7 @@
         <v>1527030000</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
@@ -5978,7 +5982,7 @@
         <v>423820000</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
@@ -6001,7 +6005,7 @@
         <v>697230000</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
@@ -6024,7 +6028,7 @@
         <v>63390000</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
@@ -6047,7 +6051,7 @@
         <v>124950000</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
@@ -6070,7 +6074,7 @@
         <v>2770000</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
@@ -6093,7 +6097,7 @@
         <v>954300000</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
@@ -6116,7 +6120,7 @@
         <v>37850000</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
@@ -6139,7 +6143,7 @@
         <v>22800000</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
@@ -6162,7 +6166,7 @@
         <v>23630000</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
@@ -6185,7 +6189,7 @@
         <v>440730000</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
@@ -6208,7 +6212,7 @@
         <v>9640000</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
@@ -6231,7 +6235,7 @@
         <v>98450000</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -6254,7 +6258,7 @@
         <v>648320000</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
@@ -6277,7 +6281,7 @@
         <v>131640000</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -6300,7 +6304,7 @@
         <v>2254090000</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -6323,7 +6327,7 @@
         <v>14400000</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -6346,7 +6350,7 @@
         <v>697580000</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -6369,7 +6373,7 @@
         <v>551030000</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
@@ -6392,7 +6396,7 @@
         <v>22620000</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -6415,7 +6419,7 @@
         <v>338930000</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
@@ -6438,7 +6442,7 @@
         <v>549450000</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>245</v>
       </c>
@@ -6461,7 +6465,7 @@
         <v>407660000</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>246</v>
       </c>
@@ -6484,7 +6488,7 @@
         <v>139160000</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>247</v>
       </c>
@@ -6507,7 +6511,7 @@
         <v>1536660000</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>248</v>
       </c>
@@ -6530,7 +6534,7 @@
         <v>421330000</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>249</v>
       </c>
@@ -6553,7 +6557,7 @@
         <v>695510000</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>250</v>
       </c>
@@ -6576,7 +6580,7 @@
         <v>60260000</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>251</v>
       </c>
@@ -6599,7 +6603,7 @@
         <v>124550000</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -6622,7 +6626,7 @@
         <v>3280000</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
@@ -6645,7 +6649,7 @@
         <v>956920000</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
@@ -6668,7 +6672,7 @@
         <v>36850000</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -6691,7 +6695,7 @@
         <v>28200000</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
@@ -6714,7 +6718,7 @@
         <v>25800000</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
@@ -6737,7 +6741,7 @@
         <v>439520000</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
@@ -6760,7 +6764,7 @@
         <v>9670000</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
@@ -6783,7 +6787,7 @@
         <v>99330000</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
@@ -6806,7 +6810,7 @@
         <v>649630000</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
@@ -6829,7 +6833,7 @@
         <v>128770000</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>262</v>
       </c>
@@ -6852,7 +6856,7 @@
         <v>2240210000</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>263</v>
       </c>
@@ -6875,7 +6879,7 @@
         <v>14700000</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
@@ -6898,7 +6902,7 @@
         <v>695440000</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>265</v>
       </c>
@@ -6921,7 +6925,7 @@
         <v>552280000</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
@@ -6944,7 +6948,7 @@
         <v>23380000</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>267</v>
       </c>
@@ -6967,7 +6971,7 @@
         <v>339420000</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
@@ -6990,7 +6994,7 @@
         <v>518080000</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
@@ -7013,7 +7017,7 @@
         <v>407240000</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
@@ -7036,7 +7040,7 @@
         <v>140580000</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
@@ -7059,7 +7063,7 @@
         <v>1540520000</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>272</v>
       </c>
@@ -7082,7 +7086,7 @@
         <v>425260000</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
@@ -7105,7 +7109,7 @@
         <v>699230000</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>274</v>
       </c>
@@ -7128,7 +7132,7 @@
         <v>58110000</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>275</v>
       </c>
@@ -7151,7 +7155,7 @@
         <v>124310000</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>276</v>
       </c>
@@ -7174,7 +7178,7 @@
         <v>4050000</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>277</v>
       </c>
@@ -7197,7 +7201,7 @@
         <v>958750000</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>278</v>
       </c>
@@ -7220,7 +7224,7 @@
         <v>36120000</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>279</v>
       </c>
@@ -7243,7 +7247,7 @@
         <v>34200000</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>280</v>
       </c>
@@ -7266,7 +7270,7 @@
         <v>26280000</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>281</v>
       </c>
@@ -7289,7 +7293,7 @@
         <v>435500000</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>282</v>
       </c>
@@ -7312,7 +7316,7 @@
         <v>12560000</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>283</v>
       </c>
@@ -7335,7 +7339,7 @@
         <v>100230000</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>284</v>
       </c>
@@ -7358,7 +7362,7 @@
         <v>648970000</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>285</v>
       </c>
@@ -7381,7 +7385,7 @@
         <v>126380000</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>286</v>
       </c>
@@ -7404,7 +7408,7 @@
         <v>2222400000</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>287</v>
       </c>
@@ -7427,7 +7431,7 @@
         <v>18190000</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>288</v>
       </c>
@@ -7450,7 +7454,7 @@
         <v>697870000</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>289</v>
       </c>
@@ -7473,7 +7477,7 @@
         <v>553760000</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>290</v>
       </c>
@@ -7496,7 +7500,7 @@
         <v>23670000</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>291</v>
       </c>
@@ -7519,7 +7523,7 @@
         <v>339280000</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>292</v>
       </c>
@@ -7542,7 +7546,7 @@
         <v>506230000</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>293</v>
       </c>
@@ -7565,7 +7569,7 @@
         <v>405950000</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>294</v>
       </c>
@@ -7588,7 +7592,7 @@
         <v>140860000</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>295</v>
       </c>
@@ -7611,7 +7615,7 @@
         <v>1561850000</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>296</v>
       </c>
@@ -7634,7 +7638,7 @@
         <v>425020000</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>297</v>
       </c>
@@ -7657,7 +7661,7 @@
         <v>697230000</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>298</v>
       </c>
@@ -7680,7 +7684,7 @@
         <v>56760000</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>299</v>
       </c>
@@ -7703,7 +7707,7 @@
         <v>124220000</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>300</v>
       </c>
@@ -7726,7 +7730,7 @@
         <v>5670000</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>301</v>
       </c>
@@ -7749,7 +7753,7 @@
         <v>959170000</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>302</v>
       </c>
@@ -7772,7 +7776,7 @@
         <v>31460000</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>303</v>
       </c>
@@ -7795,7 +7799,7 @@
         <v>39410000</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>304</v>
       </c>
@@ -7818,7 +7822,7 @@
         <v>29680000</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>305</v>
       </c>
@@ -7841,7 +7845,7 @@
         <v>433090000</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>306</v>
       </c>
@@ -7864,7 +7868,7 @@
         <v>14600000</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>307</v>
       </c>
@@ -7887,7 +7891,7 @@
         <v>100580000</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>308</v>
       </c>
@@ -7910,7 +7914,7 @@
         <v>650280000</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>309</v>
       </c>
@@ -7933,7 +7937,7 @@
         <v>127390000</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>310</v>
       </c>
@@ -7956,7 +7960,7 @@
         <v>2218620000</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>311</v>
       </c>
@@ -7979,7 +7983,7 @@
         <v>16790000</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>312</v>
       </c>
@@ -8002,7 +8006,7 @@
         <v>701470000</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>313</v>
       </c>
@@ -8025,7 +8029,7 @@
         <v>554290000</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>314</v>
       </c>
@@ -8048,7 +8052,7 @@
         <v>21890000</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>315</v>
       </c>
@@ -8071,7 +8075,7 @@
         <v>335210000</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>316</v>
       </c>
@@ -8094,7 +8098,7 @@
         <v>510000000</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>317</v>
       </c>
@@ -8117,7 +8121,7 @@
         <v>404880000</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>318</v>
       </c>
@@ -8140,7 +8144,7 @@
         <v>140770000</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>319</v>
       </c>
@@ -8163,7 +8167,7 @@
         <v>1576790000</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>320</v>
       </c>
@@ -8186,7 +8190,7 @@
         <v>422750000</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>321</v>
       </c>
@@ -8209,7 +8213,7 @@
         <v>694050000</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>322</v>
       </c>
@@ -8232,7 +8236,7 @@
         <v>55940000</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>323</v>
       </c>
@@ -8255,7 +8259,7 @@
         <v>124060000</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>324</v>
       </c>
@@ -8278,7 +8282,7 @@
         <v>6720000</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>325</v>
       </c>
@@ -8301,7 +8305,7 @@
         <v>956380000</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>326</v>
       </c>
@@ -8324,7 +8328,7 @@
         <v>30160000</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>327</v>
       </c>
@@ -8347,7 +8351,7 @@
         <v>42850000</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>328</v>
       </c>
@@ -8370,7 +8374,7 @@
         <v>35230000</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>329</v>
       </c>
@@ -8393,7 +8397,7 @@
         <v>431480000</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>330</v>
       </c>
@@ -8416,7 +8420,7 @@
         <v>16170000</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>331</v>
       </c>
@@ -8439,7 +8443,7 @@
         <v>99910000</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>332</v>
       </c>
@@ -8462,7 +8466,7 @@
         <v>651370000</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>333</v>
       </c>
@@ -8485,7 +8489,7 @@
         <v>127840000</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>334</v>
       </c>
@@ -8508,7 +8512,7 @@
         <v>2212990000</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>335</v>
       </c>
@@ -8531,7 +8535,7 @@
         <v>13830000</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>336</v>
       </c>
@@ -8554,7 +8558,7 @@
         <v>688110000</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>337</v>
       </c>
@@ -8577,7 +8581,7 @@
         <v>555360000</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>338</v>
       </c>
@@ -8600,7 +8604,7 @@
         <v>22580000</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>339</v>
       </c>
@@ -8623,7 +8627,7 @@
         <v>330870000</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>340</v>
       </c>
@@ -8646,7 +8650,7 @@
         <v>509530000</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>341</v>
       </c>
@@ -8669,7 +8673,7 @@
         <v>401050000</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>342</v>
       </c>
@@ -8692,7 +8696,7 @@
         <v>142330000</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>343</v>
       </c>
@@ -8715,7 +8719,7 @@
         <v>1577440000</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>344</v>
       </c>
@@ -8738,7 +8742,7 @@
         <v>425260000</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>345</v>
       </c>
@@ -8761,7 +8765,7 @@
         <v>702700000</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>346</v>
       </c>
@@ -8784,7 +8788,7 @@
         <v>54820000</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>347</v>
       </c>
@@ -8807,7 +8811,7 @@
         <v>123750000</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>348</v>
       </c>
@@ -8830,7 +8834,7 @@
         <v>6520000</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>349</v>
       </c>
@@ -8853,7 +8857,7 @@
         <v>953630000</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>350</v>
       </c>
@@ -8876,7 +8880,7 @@
         <v>29100000</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>351</v>
       </c>
@@ -8899,7 +8903,7 @@
         <v>31160000</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>352</v>
       </c>
@@ -8922,7 +8926,7 @@
         <v>49340000</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>353</v>
       </c>
@@ -8945,7 +8949,7 @@
         <v>428280000</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>354</v>
       </c>
@@ -8968,7 +8972,7 @@
         <v>15710000</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>355</v>
       </c>
@@ -8991,7 +8995,7 @@
         <v>99700000</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>356</v>
       </c>
@@ -9014,7 +9018,7 @@
         <v>646150000</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>357</v>
       </c>
@@ -9037,7 +9041,7 @@
         <v>128240000</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>358</v>
       </c>
@@ -9060,7 +9064,7 @@
         <v>2204500000</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>359</v>
       </c>
@@ -9083,7 +9087,7 @@
         <v>15970000</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>360</v>
       </c>
@@ -9106,7 +9110,7 @@
         <v>675430000</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>361</v>
       </c>
@@ -9129,7 +9133,7 @@
         <v>558130000</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>362</v>
       </c>
@@ -9152,7 +9156,7 @@
         <v>22560000</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>363</v>
       </c>
@@ -9175,7 +9179,7 @@
         <v>329580000</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>364</v>
       </c>
@@ -9198,7 +9202,7 @@
         <v>504820000</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>365</v>
       </c>
@@ -9221,7 +9225,7 @@
         <v>398710000</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>366</v>
       </c>
@@ -9244,7 +9248,7 @@
         <v>143860000</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>367</v>
       </c>
@@ -9267,7 +9271,7 @@
         <v>1580040000</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>368</v>
       </c>
@@ -9290,7 +9294,7 @@
         <v>424300000</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>369</v>
       </c>
@@ -9313,7 +9317,7 @@
         <v>704710000</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>370</v>
       </c>
@@ -9336,7 +9340,7 @@
         <v>52440000</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>371</v>
       </c>
@@ -9359,7 +9363,7 @@
         <v>123740000</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>372</v>
       </c>
@@ -9382,7 +9386,7 @@
         <v>5230000</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>373</v>
       </c>
@@ -9405,7 +9409,7 @@
         <v>950430000</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>374</v>
       </c>
@@ -9428,7 +9432,7 @@
         <v>27410000</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>375</v>
       </c>
@@ -9451,7 +9455,7 @@
         <v>37150000</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>376</v>
       </c>
@@ -9474,7 +9478,7 @@
         <v>37060000</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>377</v>
       </c>
@@ -9497,7 +9501,7 @@
         <v>425480000</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>378</v>
       </c>
@@ -9520,7 +9524,7 @@
         <v>13920000</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>379</v>
       </c>
@@ -9543,7 +9547,7 @@
         <v>99160000</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>380</v>
       </c>
@@ -9566,7 +9570,7 @@
         <v>641370000</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>381</v>
       </c>
@@ -9589,7 +9593,7 @@
         <v>129140000</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>382</v>
       </c>
@@ -9612,7 +9616,7 @@
         <v>2196060000</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>383</v>
       </c>
@@ -9635,7 +9639,7 @@
         <v>17840000</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>384</v>
       </c>
@@ -9658,7 +9662,7 @@
         <v>660930000</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>385</v>
       </c>
@@ -9681,7 +9685,7 @@
         <v>559330000</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>386</v>
       </c>
@@ -9704,7 +9708,7 @@
         <v>22740000</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>387</v>
       </c>
@@ -9727,7 +9731,7 @@
         <v>329250000</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>388</v>
       </c>
@@ -9750,7 +9754,7 @@
         <v>502470000</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>389</v>
       </c>
@@ -9773,7 +9777,7 @@
         <v>397710000</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>390</v>
       </c>
@@ -9796,7 +9800,7 @@
         <v>143960000</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>391</v>
       </c>
@@ -9819,7 +9823,7 @@
         <v>1590490000</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>392</v>
       </c>
@@ -9842,7 +9846,7 @@
         <v>422040000</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>393</v>
       </c>
@@ -9865,7 +9869,7 @@
         <v>703370000</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>394</v>
       </c>
@@ -9888,7 +9892,7 @@
         <v>48950000</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>395</v>
       </c>
@@ -9911,7 +9915,7 @@
         <v>123580000</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>396</v>
       </c>
@@ -9934,7 +9938,7 @@
         <v>4050000</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>397</v>
       </c>
@@ -9957,7 +9961,7 @@
         <v>948370000</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>398</v>
       </c>
@@ -9980,7 +9984,7 @@
         <v>24630000</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>399</v>
       </c>
@@ -10003,7 +10007,7 @@
         <v>31020000</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>400</v>
       </c>
@@ -10026,7 +10030,7 @@
         <v>51020000</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>401</v>
       </c>
@@ -10049,7 +10053,7 @@
         <v>424680000</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>402</v>
       </c>
@@ -10072,7 +10076,7 @@
         <v>11900000</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>403</v>
       </c>
@@ -10095,7 +10099,7 @@
         <v>99200000</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>404</v>
       </c>
@@ -10118,7 +10122,7 @@
         <v>639850000</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>405</v>
       </c>
@@ -10141,7 +10145,7 @@
         <v>130050000</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>406</v>
       </c>
@@ -10164,7 +10168,7 @@
         <v>2194930000</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>407</v>
       </c>
@@ -10187,7 +10191,7 @@
         <v>14410000</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>408</v>
       </c>
@@ -10210,7 +10214,7 @@
         <v>659570000</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>409</v>
       </c>
@@ -10233,7 +10237,7 @@
         <v>560790000</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>410</v>
       </c>
@@ -10256,7 +10260,7 @@
         <v>23990000</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>411</v>
       </c>
@@ -10279,7 +10283,7 @@
         <v>329190000</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>412</v>
       </c>
@@ -10302,7 +10306,7 @@
         <v>497340000</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>413</v>
       </c>
@@ -10325,7 +10329,7 @@
         <v>397400000</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>414</v>
       </c>
@@ -10348,7 +10352,7 @@
         <v>143960000</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>415</v>
       </c>
@@ -10371,7 +10375,7 @@
         <v>1594410000</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>416</v>
       </c>
@@ -10394,7 +10398,7 @@
         <v>421810000</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>417</v>
       </c>
@@ -10417,7 +10421,7 @@
         <v>712510000</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>418</v>
       </c>
@@ -10440,7 +10444,7 @@
         <v>46870000</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>419</v>
       </c>
@@ -10463,7 +10467,7 @@
         <v>123340000</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>420</v>
       </c>
@@ -10486,7 +10490,7 @@
         <v>5420000</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>421</v>
       </c>
@@ -10509,7 +10513,7 @@
         <v>944920000</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>422</v>
       </c>
@@ -10532,7 +10536,7 @@
         <v>23170000</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>423</v>
       </c>
@@ -10555,7 +10559,7 @@
         <v>36580000</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>424</v>
       </c>
@@ -10578,7 +10582,7 @@
         <v>43430000</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>425</v>
       </c>
@@ -10601,7 +10605,7 @@
         <v>422200000</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>426</v>
       </c>
@@ -10624,7 +10628,7 @@
         <v>15210000</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>427</v>
       </c>
@@ -10647,7 +10651,7 @@
         <v>99110000</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>428</v>
       </c>
@@ -10670,7 +10674,7 @@
         <v>637260000</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>429</v>
       </c>
@@ -10693,7 +10697,7 @@
         <v>131320000</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>430</v>
       </c>
@@ -10716,7 +10720,7 @@
         <v>2182220000</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>431</v>
       </c>
@@ -10739,7 +10743,7 @@
         <v>11880000</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>432</v>
       </c>
@@ -10762,7 +10766,7 @@
         <v>653420000</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>433</v>
       </c>
@@ -10785,7 +10789,7 @@
         <v>562610000</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>434</v>
       </c>
@@ -10808,7 +10812,7 @@
         <v>25590000</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>435</v>
       </c>
@@ -10831,7 +10835,7 @@
         <v>330390000</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>436</v>
       </c>
@@ -10854,7 +10858,7 @@
         <v>509530000</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>437</v>
       </c>
@@ -10877,7 +10881,7 @@
         <v>397250000</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>438</v>
       </c>
@@ -10900,7 +10904,7 @@
         <v>150620000</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>439</v>
       </c>
@@ -10923,7 +10927,7 @@
         <v>1605550000</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>440</v>
       </c>
@@ -10946,7 +10950,7 @@
         <v>424180000</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>441</v>
       </c>
@@ -10969,7 +10973,7 @@
         <v>710350000</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>442</v>
       </c>
@@ -10992,7 +10996,7 @@
         <v>46050000</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>443</v>
       </c>
@@ -11015,7 +11019,7 @@
         <v>123090000</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>444</v>
       </c>
@@ -11038,7 +11042,7 @@
         <v>5740000</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>445</v>
       </c>
@@ -11061,7 +11065,7 @@
         <v>940940000</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>446</v>
       </c>
@@ -11084,7 +11088,7 @@
         <v>28260000</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>447</v>
       </c>
@@ -11107,7 +11111,7 @@
         <v>20980000</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>448</v>
       </c>
@@ -11130,7 +11134,7 @@
         <v>60520000</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>449</v>
       </c>
@@ -11153,7 +11157,7 @@
         <v>421330000</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>450</v>
       </c>
@@ -11176,7 +11180,7 @@
         <v>13310000</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>451</v>
       </c>
@@ -11199,7 +11203,7 @@
         <v>99380000</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>452</v>
       </c>
@@ -11222,7 +11226,7 @@
         <v>637130000</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>453</v>
       </c>
@@ -11245,7 +11249,7 @@
         <v>132700000</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>454</v>
       </c>
@@ -11268,7 +11272,7 @@
         <v>2175940000</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>455</v>
       </c>
@@ -11291,7 +11295,7 @@
         <v>13700000</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>456</v>
       </c>
@@ -11314,7 +11318,7 @@
         <v>647910000</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>457</v>
       </c>
@@ -11337,7 +11341,7 @@
         <v>563980000</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>458</v>
       </c>
@@ -11360,7 +11364,7 @@
         <v>27100000</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>459</v>
       </c>
@@ -11383,7 +11387,7 @@
         <v>331130000</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>460</v>
       </c>
@@ -11406,7 +11410,7 @@
         <v>524320000</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>461</v>
       </c>
@@ -11429,7 +11433,7 @@
         <v>397120000</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>462</v>
       </c>
@@ -11452,7 +11456,7 @@
         <v>152390000</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>463</v>
       </c>
@@ -11475,7 +11479,7 @@
         <v>1602270000</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>464</v>
       </c>
@@ -11498,7 +11502,7 @@
         <v>425610000</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>465</v>
       </c>
@@ -11521,7 +11525,7 @@
         <v>703770000</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>466</v>
       </c>
@@ -11544,7 +11548,7 @@
         <v>50400000</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>467</v>
       </c>
@@ -11567,7 +11571,7 @@
         <v>122850000</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>468</v>
       </c>
@@ -11590,7 +11594,7 @@
         <v>7790000</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>469</v>
       </c>
@@ -11613,7 +11617,7 @@
         <v>941970000</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>470</v>
       </c>
@@ -11636,7 +11640,7 @@
         <v>34890000</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>471</v>
       </c>
@@ -11659,7 +11663,7 @@
         <v>28980000</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>472</v>
       </c>
@@ -11682,7 +11686,7 @@
         <v>48010000</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>473</v>
       </c>
@@ -11705,7 +11709,7 @@
         <v>421090000</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>474</v>
       </c>
@@ -11728,7 +11732,7 @@
         <v>14530000</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>475</v>
       </c>
@@ -11751,7 +11755,7 @@
         <v>101240000</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>476</v>
       </c>
@@ -11774,7 +11778,7 @@
         <v>634670000</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>477</v>
       </c>
@@ -11797,7 +11801,7 @@
         <v>135330000</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>478</v>
       </c>
@@ -11820,7 +11824,7 @@
         <v>2180900000</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>479</v>
       </c>
@@ -11843,7 +11847,7 @@
         <v>17120000</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>480</v>
       </c>
@@ -11866,7 +11870,7 @@
         <v>651060000</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>481</v>
       </c>
@@ -11889,7 +11893,7 @@
         <v>565260000</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>482</v>
       </c>
@@ -11912,7 +11916,7 @@
         <v>24940000</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>483</v>
       </c>
@@ -11935,7 +11939,7 @@
         <v>331610000</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>484</v>
       </c>
@@ -11958,7 +11962,7 @@
         <v>535040000</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>485</v>
       </c>
@@ -11981,7 +11985,7 @@
         <v>396800000</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>486</v>
       </c>
@@ -12004,7 +12008,7 @@
         <v>152540000</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>487</v>
       </c>
@@ -12027,7 +12031,7 @@
         <v>1608830000</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>488</v>
       </c>
@@ -12050,7 +12054,7 @@
         <v>420380000</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>489</v>
       </c>
@@ -12073,7 +12077,7 @@
         <v>703910000</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>490</v>
       </c>
@@ -12096,7 +12100,7 @@
         <v>52020000</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>491</v>
       </c>
@@ -12119,7 +12123,7 @@
         <v>122450000</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>492</v>
       </c>
@@ -12142,7 +12146,7 @@
         <v>8060000</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>493</v>
       </c>
@@ -12165,7 +12169,7 @@
         <v>943170000</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>494</v>
       </c>
@@ -12188,7 +12192,7 @@
         <v>33110000</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>495</v>
       </c>
@@ -12211,7 +12215,7 @@
         <v>36130000</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>496</v>
       </c>
@@ -12234,7 +12238,7 @@
         <v>52870000</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>497</v>
       </c>
@@ -12257,7 +12261,7 @@
         <v>417190000</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>498</v>
       </c>
@@ -12280,7 +12284,7 @@
         <v>20620000</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>499</v>
       </c>
@@ -12303,7 +12307,7 @@
         <v>102050000</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>500</v>
       </c>
@@ -12326,7 +12330,7 @@
         <v>631430000</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>501</v>
       </c>
@@ -12349,7 +12353,7 @@
         <v>137400000</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>502</v>
       </c>
@@ -12372,7 +12376,7 @@
         <v>2185880000</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>503</v>
       </c>
@@ -12395,7 +12399,7 @@
         <v>14510000</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>504</v>
       </c>
@@ -12418,7 +12422,7 @@
         <v>656240000</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>505</v>
       </c>
@@ -12441,7 +12445,7 @@
         <v>565950000</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>506</v>
       </c>
@@ -12464,7 +12468,7 @@
         <v>24300000</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>507</v>
       </c>
@@ -12487,7 +12491,7 @@
         <v>330660000</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>508</v>
       </c>
@@ -12510,7 +12514,7 @@
         <v>546940000</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>509</v>
       </c>
@@ -12533,7 +12537,7 @@
         <v>396380000</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>510</v>
       </c>
@@ -12556,7 +12560,7 @@
         <v>152640000</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>511</v>
       </c>
@@ -12579,7 +12583,7 @@
         <v>1616730000</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>512</v>
       </c>
@@ -12602,7 +12606,7 @@
         <v>417890000</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>513</v>
       </c>
@@ -12625,7 +12629,7 @@
         <v>704580000</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>514</v>
       </c>
@@ -12648,7 +12652,7 @@
         <v>56430000</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>515</v>
       </c>
@@ -12671,7 +12675,7 @@
         <v>122210000</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>516</v>
       </c>
@@ -12694,7 +12698,7 @@
         <v>7790000</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>517</v>
       </c>
@@ -12717,7 +12721,7 @@
         <v>939550000</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>518</v>
       </c>
@@ -12740,7 +12744,7 @@
         <v>31890000</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>519</v>
       </c>
@@ -12763,7 +12767,7 @@
         <v>41580000</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>520</v>
       </c>
@@ -12786,7 +12790,7 @@
         <v>52360000</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>521</v>
       </c>
@@ -12809,7 +12813,7 @@
         <v>411170000</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>522</v>
       </c>
@@ -12832,7 +12836,7 @@
         <v>18050000</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>523</v>
       </c>
@@ -12855,7 +12859,7 @@
         <v>101900000</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>524</v>
       </c>
@@ -12878,7 +12882,7 @@
         <v>628640000</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>525</v>
       </c>
@@ -12901,7 +12905,7 @@
         <v>138820000</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>526</v>
       </c>
@@ -12924,7 +12928,7 @@
         <v>2187100000</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>527</v>
       </c>
@@ -12947,7 +12951,7 @@
         <v>11720000</v>
       </c>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>528</v>
       </c>
@@ -12970,7 +12974,7 @@
         <v>651390000</v>
       </c>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>529</v>
       </c>
@@ -12993,7 +12997,7 @@
         <v>567090000</v>
       </c>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>530</v>
       </c>
@@ -13016,7 +13020,7 @@
         <v>27550000</v>
       </c>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>531</v>
       </c>
@@ -13039,7 +13043,7 @@
         <v>331790000</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>532</v>
       </c>
@@ -13062,7 +13066,7 @@
         <v>552480000</v>
       </c>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>533</v>
       </c>
@@ -13085,7 +13089,7 @@
         <v>396590000</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>534</v>
       </c>
@@ -13108,7 +13112,7 @@
         <v>158540000</v>
       </c>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>535</v>
       </c>
@@ -13131,7 +13135,7 @@
         <v>1625310000</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>536</v>
       </c>
@@ -13154,7 +13158,7 @@
         <v>435580000</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>537</v>
       </c>
@@ -13177,7 +13181,7 @@
         <v>712510000</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>538</v>
       </c>
@@ -13200,7 +13204,7 @@
         <v>60520000</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>539</v>
       </c>
@@ -13223,7 +13227,7 @@
         <v>122370000</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>540</v>
       </c>
@@ -13246,7 +13250,7 @@
         <v>8740000</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>541</v>
       </c>
@@ -13269,7 +13273,7 @@
         <v>944380000</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>542</v>
       </c>
@@ -13292,7 +13296,7 @@
         <v>34620000</v>
       </c>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>543</v>
       </c>
@@ -13315,7 +13319,7 @@
         <v>51470000</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>544</v>
       </c>
@@ -13338,7 +13342,7 @@
         <v>53200000</v>
       </c>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>545</v>
       </c>
@@ -13361,7 +13365,7 @@
         <v>410380000</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>546</v>
       </c>
@@ -13384,7 +13388,7 @@
         <v>19510000</v>
       </c>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>547</v>
       </c>
@@ -13407,7 +13411,7 @@
         <v>101320000</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>548</v>
       </c>
@@ -13430,7 +13434,7 @@
         <v>625630000</v>
       </c>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>549</v>
       </c>
@@ -13453,7 +13457,7 @@
         <v>141700000</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>550</v>
       </c>
@@ -13476,7 +13480,7 @@
         <v>2208800000</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>551</v>
       </c>
@@ -13499,7 +13503,7 @@
         <v>10580000</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>552</v>
       </c>
@@ -13522,7 +13526,7 @@
         <v>645220000</v>
       </c>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>553</v>
       </c>
@@ -13545,7 +13549,7 @@
         <v>569620000</v>
       </c>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>554</v>
       </c>
@@ -13568,7 +13572,7 @@
         <v>27680000</v>
       </c>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>555</v>
       </c>
@@ -13591,7 +13595,7 @@
         <v>330890000</v>
       </c>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>556</v>
       </c>
@@ -13614,7 +13618,7 @@
         <v>573540000</v>
       </c>
     </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>557</v>
       </c>
@@ -13637,7 +13641,7 @@
         <v>396380000</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>558</v>
       </c>
@@ -13660,7 +13664,7 @@
         <v>159760000</v>
       </c>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>559</v>
       </c>
@@ -13683,7 +13687,7 @@
         <v>1649230000</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>560</v>
       </c>
@@ -13706,7 +13710,7 @@
         <v>426570000</v>
       </c>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>561</v>
       </c>
@@ -13729,7 +13733,7 @@
         <v>699360000</v>
       </c>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>562</v>
       </c>
@@ -13752,7 +13756,7 @@
         <v>68130000</v>
       </c>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>563</v>
       </c>
@@ -13775,7 +13779,7 @@
         <v>122530000</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>564</v>
       </c>
@@ -13798,7 +13802,7 @@
         <v>10520000</v>
       </c>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>565</v>
       </c>
@@ -13821,7 +13825,7 @@
         <v>945580000</v>
       </c>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>566</v>
       </c>
@@ -13844,7 +13848,7 @@
         <v>34320000</v>
       </c>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>567</v>
       </c>
@@ -13867,7 +13871,7 @@
         <v>61020000</v>
       </c>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>568</v>
       </c>
@@ -13890,7 +13894,7 @@
         <v>61360000</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>569</v>
       </c>
@@ -13913,7 +13917,7 @@
         <v>409190000</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>570</v>
       </c>
@@ -13936,7 +13940,7 @@
         <v>19000000</v>
       </c>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>571</v>
       </c>
@@ -13959,7 +13963,7 @@
         <v>103520000</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>572</v>
       </c>
@@ -13982,7 +13986,7 @@
         <v>624770000</v>
       </c>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>573</v>
       </c>
@@ -14005,7 +14009,7 @@
         <v>146900000</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>574</v>
       </c>
@@ -14028,7 +14032,7 @@
         <v>2240910000</v>
       </c>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>575</v>
       </c>
@@ -14051,7 +14055,7 @@
         <v>12300000</v>
       </c>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>576</v>
       </c>
@@ -14074,7 +14078,7 @@
         <v>645160000</v>
       </c>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>577</v>
       </c>
@@ -14097,7 +14101,7 @@
         <v>571660000</v>
       </c>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>578</v>
       </c>
@@ -14120,7 +14124,7 @@
         <v>25240000</v>
       </c>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>579</v>
       </c>
@@ -14143,7 +14147,7 @@
         <v>330890000</v>
       </c>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>580</v>
       </c>
@@ -14166,7 +14170,7 @@
         <v>585640000</v>
       </c>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>581</v>
       </c>
@@ -14189,7 +14193,7 @@
         <v>396170000</v>
       </c>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>582</v>
       </c>
@@ -14212,7 +14216,7 @@
         <v>160060000</v>
       </c>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>583</v>
       </c>
@@ -14235,7 +14239,7 @@
         <v>1658680000</v>
       </c>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>584</v>
       </c>
@@ -14258,7 +14262,7 @@
         <v>425490000</v>
       </c>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>585</v>
       </c>
@@ -14281,7 +14285,7 @@
         <v>696040000</v>
       </c>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>586</v>
       </c>
@@ -14304,7 +14308,7 @@
         <v>69290000</v>
       </c>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>587</v>
       </c>
@@ -14327,7 +14331,7 @@
         <v>122210000</v>
       </c>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>588</v>
       </c>
@@ -14350,7 +14354,7 @@
         <v>10310000</v>
       </c>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>589</v>
       </c>
@@ -14373,7 +14377,7 @@
         <v>948610000</v>
       </c>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>590</v>
       </c>
@@ -14396,7 +14400,7 @@
         <v>34420000</v>
       </c>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>591</v>
       </c>
@@ -14419,7 +14423,7 @@
         <v>46970000</v>
       </c>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>592</v>
       </c>
@@ -14442,7 +14446,7 @@
         <v>81580000</v>
       </c>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594">
         <v>593</v>
       </c>
@@ -14465,7 +14469,7 @@
         <v>408400000</v>
       </c>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>594</v>
       </c>
@@ -14488,7 +14492,7 @@
         <v>20620000</v>
       </c>
     </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596">
         <v>595</v>
       </c>
@@ -14511,7 +14515,7 @@
         <v>104890000</v>
       </c>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>596</v>
       </c>
@@ -14534,7 +14538,7 @@
         <v>622630000</v>
       </c>
     </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598">
         <v>597</v>
       </c>
@@ -14557,7 +14561,7 @@
         <v>145180000</v>
       </c>
     </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>598</v>
       </c>
@@ -14580,7 +14584,7 @@
         <v>2244780000</v>
       </c>
     </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600">
         <v>599</v>
       </c>
@@ -14603,7 +14607,7 @@
         <v>12890000</v>
       </c>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>600</v>
       </c>
@@ -14626,7 +14630,7 @@
         <v>647570000</v>
       </c>
     </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602">
         <v>601</v>
       </c>
@@ -14649,7 +14653,7 @@
         <v>572080000</v>
       </c>
     </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603">
         <v>602</v>
       </c>
@@ -14672,7 +14676,7 @@
         <v>26050000</v>
       </c>
     </row>
-    <row r="604" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604">
         <v>603</v>
       </c>
@@ -14695,7 +14699,7 @@
         <v>330730000</v>
       </c>
     </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605">
         <v>604</v>
       </c>
@@ -14718,7 +14722,7 @@
         <v>593090000</v>
       </c>
     </row>
-    <row r="606" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606">
         <v>605</v>
       </c>
@@ -14741,7 +14745,7 @@
         <v>396380000</v>
       </c>
     </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607">
         <v>606</v>
       </c>
@@ -14764,7 +14768,7 @@
         <v>161690000</v>
       </c>
     </row>
-    <row r="608" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608">
         <v>607</v>
       </c>
@@ -14787,7 +14791,7 @@
         <v>1666820000</v>
       </c>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609">
         <v>608</v>
       </c>
@@ -14810,7 +14814,7 @@
         <v>431360000</v>
       </c>
     </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610">
         <v>609</v>
       </c>
@@ -14833,7 +14837,7 @@
         <v>698430000</v>
       </c>
     </row>
-    <row r="611" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611">
         <v>610</v>
       </c>
@@ -14856,7 +14860,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612">
         <v>611</v>
       </c>
@@ -14879,7 +14883,7 @@
         <v>121890000</v>
       </c>
     </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613">
         <v>612</v>
       </c>
@@ -14902,7 +14906,7 @@
         <v>9280000</v>
       </c>
     </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614">
         <v>613</v>
       </c>
@@ -14925,7 +14929,7 @@
         <v>951640000</v>
       </c>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615">
         <v>614</v>
       </c>
@@ -14948,7 +14952,7 @@
         <v>35440000</v>
       </c>
     </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616">
         <v>615</v>
       </c>
@@ -14971,7 +14975,7 @@
         <v>53340000</v>
       </c>
     </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617">
         <v>616</v>
       </c>
@@ -14994,7 +14998,7 @@
         <v>71310000</v>
       </c>
     </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618">
         <v>617</v>
       </c>
@@ -15017,7 +15021,7 @@
         <v>407220000</v>
       </c>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619">
         <v>618</v>
       </c>
@@ -15040,7 +15044,7 @@
         <v>21340000</v>
       </c>
     </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620">
         <v>619</v>
       </c>
@@ -15063,7 +15067,7 @@
         <v>106050000</v>
       </c>
     </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621">
         <v>620</v>
       </c>
@@ -15086,7 +15090,7 @@
         <v>619630000</v>
       </c>
     </row>
-    <row r="622" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622">
         <v>621</v>
       </c>
@@ -15109,7 +15113,7 @@
         <v>145760000</v>
       </c>
     </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623">
         <v>622</v>
       </c>
@@ -15132,7 +15136,7 @@
         <v>2251820000</v>
       </c>
     </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624">
         <v>623</v>
       </c>
@@ -15155,7 +15159,7 @@
         <v>10430000</v>
       </c>
     </row>
-    <row r="625" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625">
         <v>624</v>
       </c>
@@ -15178,7 +15182,7 @@
         <v>653980000</v>
       </c>
     </row>
-    <row r="626" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626">
         <v>625</v>
       </c>
@@ -15201,7 +15205,7 @@
         <v>573400000</v>
       </c>
     </row>
-    <row r="627" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627">
         <v>626</v>
       </c>
@@ -15224,7 +15228,7 @@
         <v>23760000</v>
       </c>
     </row>
-    <row r="628" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628">
         <v>627</v>
       </c>
@@ -15247,7 +15251,7 @@
         <v>330570000</v>
       </c>
     </row>
-    <row r="629" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629">
         <v>628</v>
       </c>
@@ -15270,7 +15274,7 @@
         <v>593630000</v>
       </c>
     </row>
-    <row r="630" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630">
         <v>629</v>
       </c>
@@ -15293,7 +15297,7 @@
         <v>395960000</v>
       </c>
     </row>
-    <row r="631" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631">
         <v>630</v>
       </c>
@@ -15316,7 +15320,7 @@
         <v>161950000</v>
       </c>
     </row>
-    <row r="632" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632">
         <v>631</v>
       </c>
@@ -15339,7 +15343,7 @@
         <v>1673630000</v>
       </c>
     </row>
-    <row r="633" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633">
         <v>632</v>
       </c>
@@ -15362,7 +15366,7 @@
         <v>427410000</v>
       </c>
     </row>
-    <row r="634" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634">
         <v>633</v>
       </c>
@@ -15385,7 +15389,7 @@
         <v>696700000</v>
       </c>
     </row>
-    <row r="635" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635">
         <v>634</v>
       </c>
@@ -15408,7 +15412,7 @@
         <v>68460000</v>
       </c>
     </row>
-    <row r="636" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636">
         <v>635</v>
       </c>
@@ -15431,7 +15435,7 @@
         <v>121650000</v>
       </c>
     </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637">
         <v>636</v>
       </c>
@@ -15454,7 +15458,7 @@
         <v>8600000</v>
       </c>
     </row>
-    <row r="638" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638">
         <v>637</v>
       </c>
@@ -15477,7 +15481,7 @@
         <v>952250000</v>
       </c>
     </row>
-    <row r="639" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639">
         <v>638</v>
       </c>
@@ -15500,7 +15504,7 @@
         <v>35440000</v>
       </c>
     </row>
-    <row r="640" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640">
         <v>639</v>
       </c>
@@ -15523,7 +15527,7 @@
         <v>55640000</v>
       </c>
     </row>
-    <row r="641" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641">
         <v>640</v>
       </c>
@@ -15546,7 +15550,7 @@
         <v>79390000</v>
       </c>
     </row>
-    <row r="642" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642">
         <v>641</v>
       </c>
@@ -15569,7 +15573,7 @@
         <v>405240000</v>
       </c>
     </row>
-    <row r="643" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643">
         <v>642</v>
       </c>
@@ -15592,7 +15596,7 @@
         <v>18580000</v>
       </c>
     </row>
-    <row r="644" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644">
         <v>643</v>
       </c>
@@ -15615,7 +15619,7 @@
         <v>103760000</v>
       </c>
     </row>
-    <row r="645" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645">
         <v>644</v>
       </c>
@@ -15638,7 +15642,7 @@
         <v>616430000</v>
       </c>
     </row>
-    <row r="646" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646">
         <v>645</v>
       </c>
@@ -15661,7 +15665,7 @@
         <v>143360000</v>
       </c>
     </row>
-    <row r="647" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647">
         <v>646</v>
       </c>
@@ -15684,7 +15688,7 @@
         <v>2249330000</v>
       </c>
     </row>
-    <row r="648" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648">
         <v>647</v>
       </c>
@@ -15707,7 +15711,7 @@
         <v>7840000</v>
       </c>
     </row>
-    <row r="649" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649">
         <v>648</v>
       </c>
@@ -15730,7 +15734,7 @@
         <v>654720000</v>
       </c>
     </row>
-    <row r="650" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650">
         <v>649</v>
       </c>
@@ -15753,7 +15757,7 @@
         <v>574020000</v>
       </c>
     </row>
-    <row r="651" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651">
         <v>650</v>
       </c>
@@ -15776,7 +15780,7 @@
         <v>24400000</v>
       </c>
     </row>
-    <row r="652" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652">
         <v>651</v>
       </c>
@@ -15799,7 +15803,7 @@
         <v>328910000</v>
       </c>
     </row>
-    <row r="653" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653">
         <v>652</v>
       </c>
@@ -15822,7 +15826,7 @@
         <v>546940000</v>
       </c>
     </row>
-    <row r="654" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654">
         <v>653</v>
       </c>
@@ -15845,7 +15849,7 @@
         <v>395740000</v>
       </c>
     </row>
-    <row r="655" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655">
         <v>654</v>
       </c>
@@ -15868,7 +15872,7 @@
         <v>161690000</v>
       </c>
     </row>
-    <row r="656" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656">
         <v>655</v>
       </c>
@@ -15891,7 +15895,7 @@
         <v>1678400000</v>
       </c>
     </row>
-    <row r="657" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657">
         <v>656</v>
       </c>
@@ -15914,7 +15918,7 @@
         <v>423110000</v>
       </c>
     </row>
-    <row r="658" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658">
         <v>657</v>
       </c>
@@ -15937,7 +15941,7 @@
         <v>695240000</v>
       </c>
     </row>
-    <row r="659" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659">
         <v>658</v>
       </c>
@@ -15960,7 +15964,7 @@
         <v>69320000</v>
       </c>
     </row>
-    <row r="660" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660">
         <v>659</v>
       </c>
@@ -15983,7 +15987,7 @@
         <v>121250000</v>
       </c>
     </row>
-    <row r="661" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661">
         <v>660</v>
       </c>
@@ -16006,7 +16010,7 @@
         <v>9900000</v>
       </c>
     </row>
-    <row r="662" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662">
         <v>661</v>
       </c>
@@ -16029,7 +16033,7 @@
         <v>951030000</v>
       </c>
     </row>
-    <row r="663" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663">
         <v>662</v>
       </c>
@@ -16052,7 +16056,7 @@
         <v>34800000</v>
       </c>
     </row>
-    <row r="664" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664">
         <v>663</v>
       </c>
@@ -16075,7 +16079,7 @@
         <v>44140000</v>
       </c>
     </row>
-    <row r="665" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665">
         <v>664</v>
       </c>
@@ -16098,7 +16102,7 @@
         <v>85350000</v>
       </c>
     </row>
-    <row r="666" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666">
         <v>665</v>
       </c>
@@ -16121,7 +16125,7 @@
         <v>405010000</v>
       </c>
     </row>
-    <row r="667" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667">
         <v>666</v>
       </c>
@@ -16144,7 +16148,7 @@
         <v>18190000</v>
       </c>
     </row>
-    <row r="668" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668">
         <v>667</v>
       </c>
@@ -16167,7 +16171,7 @@
         <v>101130000</v>
       </c>
     </row>
-    <row r="669" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669">
         <v>668</v>
       </c>
@@ -16190,7 +16194,7 @@
         <v>613240000</v>
       </c>
     </row>
-    <row r="670" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670">
         <v>669</v>
       </c>
@@ -16213,7 +16217,7 @@
         <v>141970000</v>
       </c>
     </row>
-    <row r="671" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671">
         <v>670</v>
       </c>
@@ -16236,7 +16240,7 @@
         <v>2236990000</v>
       </c>
     </row>
-    <row r="672" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672">
         <v>671</v>
       </c>
@@ -16259,7 +16263,7 @@
         <v>9840000</v>
       </c>
     </row>
-    <row r="673" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673">
         <v>672</v>
       </c>
@@ -16282,7 +16286,7 @@
         <v>652350000</v>
       </c>
     </row>
-    <row r="674" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674">
         <v>673</v>
       </c>
@@ -16305,7 +16309,7 @@
         <v>574280000</v>
       </c>
     </row>
-    <row r="675" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675">
         <v>674</v>
       </c>
@@ -16328,7 +16332,7 @@
         <v>25100000</v>
       </c>
     </row>
-    <row r="676" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676">
         <v>675</v>
       </c>
@@ -16351,7 +16355,7 @@
         <v>328530000</v>
       </c>
     </row>
-    <row r="677" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677">
         <v>676</v>
       </c>
@@ -16374,7 +16378,7 @@
         <v>530140000</v>
       </c>
     </row>
-    <row r="678" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678">
         <v>677</v>
       </c>
@@ -16397,7 +16401,7 @@
         <v>395320000</v>
       </c>
     </row>
-    <row r="679" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679">
         <v>678</v>
       </c>
@@ -16420,7 +16424,7 @@
         <v>162200000</v>
       </c>
     </row>
-    <row r="680" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680">
         <v>679</v>
       </c>
@@ -16443,7 +16447,7 @@
         <v>1681130000</v>
       </c>
     </row>
-    <row r="681" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681">
         <v>680</v>
       </c>
@@ -16466,7 +16470,7 @@
         <v>421090000</v>
       </c>
     </row>
-    <row r="682" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682">
         <v>681</v>
       </c>
@@ -16489,7 +16493,7 @@
         <v>696440000</v>
       </c>
     </row>
-    <row r="683" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683">
         <v>682</v>
       </c>
@@ -16512,7 +16516,7 @@
         <v>68890000</v>
       </c>
     </row>
-    <row r="684" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684">
         <v>683</v>
       </c>
@@ -16535,7 +16539,7 @@
         <v>120850000</v>
       </c>
     </row>
-    <row r="685" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685">
         <v>684</v>
       </c>
@@ -16558,7 +16562,7 @@
         <v>9490000</v>
       </c>
     </row>
-    <row r="686" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686">
         <v>685</v>
       </c>
@@ -16581,7 +16585,7 @@
         <v>950430000</v>
       </c>
     </row>
-    <row r="687" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687">
         <v>686</v>
       </c>
@@ -16604,7 +16608,7 @@
         <v>37870000</v>
       </c>
     </row>
-    <row r="688" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688">
         <v>687</v>
       </c>
@@ -16627,7 +16631,7 @@
         <v>50780000</v>
       </c>
     </row>
-    <row r="689" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689">
         <v>688</v>
       </c>
@@ -16650,7 +16654,7 @@
         <v>81420000</v>
       </c>
     </row>
-    <row r="690" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690">
         <v>689</v>
       </c>
@@ -16673,7 +16677,7 @@
         <v>403440000</v>
       </c>
     </row>
-    <row r="691" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691">
         <v>690</v>
       </c>
@@ -16696,7 +16700,7 @@
         <v>14250000</v>
       </c>
     </row>
-    <row r="692" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692">
         <v>691</v>
       </c>
@@ -16719,7 +16723,7 @@
         <v>98670000</v>
       </c>
     </row>
-    <row r="693" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693">
         <v>692</v>
       </c>
@@ -16742,7 +16746,7 @@
         <v>608350000</v>
       </c>
     </row>
-    <row r="694" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694">
         <v>693</v>
       </c>
@@ -16765,7 +16769,7 @@
         <v>140840000</v>
       </c>
     </row>
-    <row r="695" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695">
         <v>694</v>
       </c>
@@ -16788,7 +16792,7 @@
         <v>2213230000</v>
       </c>
     </row>
-    <row r="696" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696">
         <v>695</v>
       </c>
@@ -16811,7 +16815,7 @@
         <v>11840000</v>
       </c>
     </row>
-    <row r="697" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697">
         <v>696</v>
       </c>
@@ -16834,7 +16838,7 @@
         <v>644210000</v>
       </c>
     </row>
-    <row r="698" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698">
         <v>697</v>
       </c>
@@ -16857,7 +16861,7 @@
         <v>575280000</v>
       </c>
     </row>
-    <row r="699" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699">
         <v>698</v>
       </c>
@@ -16880,7 +16884,7 @@
         <v>22860000</v>
       </c>
     </row>
-    <row r="700" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700">
         <v>699</v>
       </c>
@@ -16903,7 +16907,7 @@
         <v>327650000</v>
       </c>
     </row>
-    <row r="701" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701">
         <v>700</v>
       </c>
@@ -16926,7 +16930,7 @@
         <v>498280000</v>
       </c>
     </row>
-    <row r="702" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702">
         <v>701</v>
       </c>
@@ -16949,7 +16953,7 @@
         <v>394690000</v>
       </c>
     </row>
-    <row r="703" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703">
         <v>702</v>
       </c>
@@ -16972,7 +16976,7 @@
         <v>164360000</v>
       </c>
     </row>
-    <row r="704" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704">
         <v>703</v>
       </c>
@@ -16995,7 +16999,7 @@
         <v>1682040000</v>
       </c>
     </row>
-    <row r="705" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705">
         <v>704</v>
       </c>
@@ -17018,7 +17022,7 @@
         <v>423820000</v>
       </c>
     </row>
-    <row r="706" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706">
         <v>705</v>
       </c>
@@ -17041,7 +17045,7 @@
         <v>702700000</v>
       </c>
     </row>
-    <row r="707" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707">
         <v>706</v>
       </c>
@@ -17064,7 +17068,7 @@
         <v>68130000</v>
       </c>
     </row>
-    <row r="708" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708">
         <v>707</v>
       </c>
@@ -17087,7 +17091,7 @@
         <v>120530000</v>
       </c>
     </row>
-    <row r="709" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709">
         <v>708</v>
       </c>
@@ -17110,7 +17114,7 @@
         <v>8940000</v>
       </c>
     </row>
-    <row r="710" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710">
         <v>709</v>
       </c>
@@ -17133,7 +17137,7 @@
         <v>947400000</v>
       </c>
     </row>
-    <row r="711" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711">
         <v>710</v>
       </c>
@@ -17156,7 +17160,7 @@
         <v>39410000</v>
       </c>
     </row>
-    <row r="712" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712">
         <v>711</v>
       </c>
@@ -17179,7 +17183,7 @@
         <v>52660000</v>
       </c>
     </row>
-    <row r="713" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713">
         <v>712</v>
       </c>
@@ -17202,7 +17206,7 @@
         <v>73960000</v>
       </c>
     </row>
-    <row r="714" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714">
         <v>713</v>
       </c>
@@ -17225,7 +17229,7 @@
         <v>401560000</v>
       </c>
     </row>
-    <row r="715" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715">
         <v>714</v>
       </c>
@@ -17248,7 +17252,7 @@
         <v>14200000</v>
       </c>
     </row>
-    <row r="716" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716">
         <v>715</v>
       </c>
@@ -17271,7 +17275,7 @@
         <v>96170000</v>
       </c>
     </row>
-    <row r="717" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717">
         <v>716</v>
       </c>
@@ -17294,7 +17298,7 @@
         <v>602840000</v>
       </c>
     </row>
-    <row r="718" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718">
         <v>717</v>
       </c>
@@ -17317,7 +17321,7 @@
         <v>139660000</v>
       </c>
     </row>
-    <row r="719" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719">
         <v>718</v>
       </c>
@@ -17340,7 +17344,7 @@
         <v>2200330000</v>
       </c>
     </row>
-    <row r="720" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720">
         <v>719</v>
       </c>
@@ -17363,7 +17367,7 @@
         <v>11550000</v>
       </c>
     </row>
-    <row r="721" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721">
         <v>720</v>
       </c>
@@ -17386,7 +17390,7 @@
         <v>626790000</v>
       </c>
     </row>
-    <row r="722" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722">
         <v>721</v>
       </c>
@@ -17409,7 +17413,7 @@
         <v>575960000</v>
       </c>
     </row>
-    <row r="723" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723">
         <v>722</v>
       </c>
@@ -17432,7 +17436,7 @@
         <v>23770000</v>
       </c>
     </row>
-    <row r="724" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724">
         <v>723</v>
       </c>
@@ -17455,7 +17459,7 @@
         <v>325490000</v>
       </c>
     </row>
-    <row r="725" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725">
         <v>724</v>
       </c>
@@ -17478,7 +17482,7 @@
         <v>506230000</v>
       </c>
     </row>
-    <row r="726" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726">
         <v>725</v>
       </c>
@@ -17501,7 +17505,7 @@
         <v>394270000</v>
       </c>
     </row>
-    <row r="727" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727">
         <v>726</v>
       </c>
@@ -17524,7 +17528,7 @@
         <v>165130000</v>
       </c>
     </row>
-    <row r="728" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728">
         <v>727</v>
       </c>
@@ -17547,7 +17551,7 @@
         <v>1687280000</v>
       </c>
     </row>
-    <row r="729" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729">
         <v>728</v>
       </c>
@@ -17570,7 +17574,7 @@
         <v>424660000</v>
       </c>
     </row>
-    <row r="730" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730">
         <v>729</v>
       </c>
@@ -17593,7 +17597,7 @@
         <v>704310000</v>
       </c>
     </row>
-    <row r="731" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731">
         <v>730</v>
       </c>
@@ -17616,7 +17620,7 @@
         <v>68930000</v>
       </c>
     </row>
-    <row r="732" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732">
         <v>731</v>
       </c>
@@ -17639,7 +17643,7 @@
         <v>120130000</v>
       </c>
     </row>
-    <row r="733" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733">
         <v>732</v>
       </c>
@@ -17662,7 +17666,7 @@
         <v>7860000</v>
       </c>
     </row>
-    <row r="734" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734">
         <v>733</v>
       </c>
@@ -17685,7 +17689,7 @@
         <v>943170000</v>
       </c>
     </row>
-    <row r="735" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735">
         <v>734</v>
       </c>
@@ -17708,7 +17712,7 @@
         <v>40960000</v>
       </c>
     </row>
-    <row r="736" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736">
         <v>735</v>
       </c>
@@ -17731,7 +17735,7 @@
         <v>42510000</v>
       </c>
     </row>
-    <row r="737" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737">
         <v>736</v>
       </c>
@@ -17754,7 +17758,7 @@
         <v>77960000</v>
       </c>
     </row>
-    <row r="738" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738">
         <v>737</v>
       </c>
@@ -17777,7 +17781,7 @@
         <v>400330000</v>
       </c>
     </row>
-    <row r="739" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739">
         <v>738</v>
       </c>
@@ -17800,7 +17804,7 @@
         <v>14170000</v>
       </c>
     </row>
-    <row r="740" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740">
         <v>739</v>
       </c>
@@ -17823,7 +17827,7 @@
         <v>93420000</v>
       </c>
     </row>
-    <row r="741" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741">
         <v>740</v>
       </c>
@@ -17846,7 +17850,7 @@
         <v>598200000</v>
       </c>
     </row>
-    <row r="742" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742">
         <v>741</v>
       </c>
@@ -17869,7 +17873,7 @@
         <v>138430000</v>
       </c>
     </row>
-    <row r="743" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743">
         <v>742</v>
       </c>
@@ -17892,7 +17896,7 @@
         <v>2190810000</v>
       </c>
     </row>
-    <row r="744" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744">
         <v>743</v>
       </c>
@@ -17915,7 +17919,7 @@
         <v>10610000</v>
       </c>
     </row>
-    <row r="745" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745">
         <v>744</v>
       </c>
@@ -17939,6 +17943,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G745" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <dateGroupItem year="2026" month="7" day="8" dateTimeGrouping="day"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
